--- a/artfynd/A 27227-2026 artfynd.xlsx
+++ b/artfynd/A 27227-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130330090</v>
+        <v>130331499</v>
       </c>
       <c r="B2" t="n">
-        <v>58236</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>757</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granhult, Gårdgölen 200 m. SV., Sm</t>
+          <t>Gårdsgölen, Granhult 200 m. SV, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483704</v>
+        <v>483721</v>
       </c>
       <c r="R2" t="n">
-        <v>6330933</v>
+        <v>6330941</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +754,14 @@
           <t>2025-12-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga  i gles äldre gran-tallskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,60 +789,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330614</v>
+        <v>131580193</v>
       </c>
       <c r="B3" t="n">
-        <v>96210</v>
+        <v>92716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>757</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdsgölen, Granhult, 200 m. VSV, Sm</t>
+          <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483672</v>
+        <v>483720</v>
       </c>
       <c r="R3" t="n">
-        <v>6330979</v>
+        <v>6330944</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,17 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en del av ett klippblock.</t>
+          <t>Porer 3 per mm. Mörkröd med KOH.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,71 +880,87 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Barklös låga # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Uno Pettersson</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Pettersson, Elin Kannerby</t>
+          <t>Per Fogelström, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130331499</v>
+        <v>130330614</v>
       </c>
       <c r="B4" t="n">
-        <v>92506</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>757</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdsgölen, Granhult 200 m. SV, Sm</t>
+          <t>Gårdsgölen, Granhult, 200 m. VSV, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483721</v>
+        <v>483672</v>
       </c>
       <c r="R4" t="n">
-        <v>6330941</v>
+        <v>6330979</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +997,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga  i gles äldre gran-tallskog.</t>
+          <t>På en del av ett klippblock.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1028,7 @@
         <v>130339296</v>
       </c>
       <c r="B5" t="n">
-        <v>91797</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,56 +1122,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339295</v>
+        <v>130330090</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogslund, Sm</t>
+          <t>Granhult, Gårdgölen 200 m. SV., Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483736</v>
+        <v>483704</v>
       </c>
       <c r="R6" t="n">
-        <v>6330924</v>
+        <v>6330933</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,9 +1202,19 @@
           <t>2025-12-28</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,22 +1229,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Uno Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Uno Pettersson</t>
+          <t>Uno Pettersson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131580193</v>
+        <v>130339295</v>
       </c>
       <c r="B7" t="n">
-        <v>92579</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,26 +1252,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>757</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1263,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483720</v>
+        <v>483736</v>
       </c>
       <c r="R7" t="n">
-        <v>6330944</v>
+        <v>6330924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,17 +1314,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Porer 3 per mm. Mörkröd med KOH.</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,37 +1328,140 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Barklös låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Fogelström, Uno Pettersson</t>
+          <t>Elin Kannerby, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131584635</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogslund, 400 m söder., Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>483690</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6330959</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Uno Pettersson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27227-2026 artfynd.xlsx
+++ b/artfynd/A 27227-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130331499</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131580193</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330614</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339296</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330090</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339295</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,8 +1497,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584635</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>